--- a/research/traditional_assets/database/data/france/france_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00681</v>
+        <v>0.0522</v>
       </c>
       <c r="E2">
-        <v>0.392</v>
+        <v>0.261</v>
       </c>
       <c r="F2">
-        <v>0.272</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1137902559867878</v>
+        <v>0.196763827028246</v>
       </c>
       <c r="H2">
-        <v>0.1137902559867878</v>
+        <v>0.196763827028246</v>
       </c>
       <c r="I2">
-        <v>0.2105147261216625</v>
+        <v>0.2025708969949822</v>
       </c>
       <c r="J2">
-        <v>0.1605769284269281</v>
+        <v>0.1515591642629319</v>
       </c>
       <c r="K2">
-        <v>256.6</v>
+        <v>256.3</v>
       </c>
       <c r="L2">
-        <v>0.1412606661161575</v>
+        <v>0.1445001973276202</v>
       </c>
       <c r="M2">
-        <v>112.3</v>
+        <v>222.23</v>
       </c>
       <c r="N2">
-        <v>0.05288438898045679</v>
+        <v>0.1148831679073614</v>
       </c>
       <c r="O2">
-        <v>0.4376461418550272</v>
+        <v>0.8670698400312133</v>
       </c>
       <c r="P2">
-        <v>95</v>
+        <v>219.7</v>
       </c>
       <c r="Q2">
-        <v>0.0447374617376972</v>
+        <v>0.1135752688172043</v>
       </c>
       <c r="R2">
-        <v>0.3702260327357755</v>
+        <v>0.8571985953960202</v>
       </c>
       <c r="S2">
-        <v>17.3</v>
+        <v>2.530000000000001</v>
       </c>
       <c r="T2">
-        <v>0.1540516473731077</v>
+        <v>0.01138460153894614</v>
       </c>
       <c r="U2">
-        <v>371.6</v>
+        <v>704</v>
       </c>
       <c r="V2">
-        <v>0.1749941134918766</v>
+        <v>0.3639371381306865</v>
       </c>
       <c r="W2">
-        <v>0.1122975929978118</v>
+        <v>0.1071801948730816</v>
       </c>
       <c r="X2">
-        <v>0.09564319545312612</v>
+        <v>0.1493918435640297</v>
       </c>
       <c r="Y2">
-        <v>0.0166543975446857</v>
+        <v>-0.04221164869094809</v>
       </c>
       <c r="Z2">
-        <v>0.3924597601814843</v>
+        <v>0.3358071905942938</v>
       </c>
       <c r="AA2">
-        <v>0.06301998282111156</v>
+        <v>0.05089465715995425</v>
       </c>
       <c r="AB2">
-        <v>0.0511238407241796</v>
+        <v>0.07889805559136959</v>
       </c>
       <c r="AC2">
-        <v>0.01189614209693195</v>
+        <v>-0.02800339843141534</v>
       </c>
       <c r="AD2">
-        <v>3441.8</v>
+        <v>3506.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3441.8</v>
+        <v>3506.1</v>
       </c>
       <c r="AG2">
-        <v>3070.2</v>
+        <v>2802.1</v>
       </c>
       <c r="AH2">
-        <v>0.6184392575422709</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="AI2">
-        <v>0.5900059998285764</v>
+        <v>0.6462618889626189</v>
       </c>
       <c r="AJ2">
-        <v>0.5911392648786029</v>
+        <v>0.5915971709067877</v>
       </c>
       <c r="AK2">
-        <v>0.5621120855379997</v>
+        <v>0.59351436075574</v>
       </c>
       <c r="AL2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AM2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AN2">
-        <v>8.623903783512905</v>
+        <v>9.658677685950414</v>
       </c>
       <c r="AO2">
-        <v>16.62608695652174</v>
+        <v>13.30740740740741</v>
       </c>
       <c r="AP2">
-        <v>7.692808819844651</v>
+        <v>7.719283746556473</v>
       </c>
       <c r="AQ2">
-        <v>16.62608695652174</v>
+        <v>13.30740740740741</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00681</v>
+        <v>0.0522</v>
       </c>
       <c r="E3">
-        <v>0.392</v>
+        <v>0.261</v>
       </c>
       <c r="F3">
-        <v>0.272</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1137902559867878</v>
+        <v>0.196763827028246</v>
       </c>
       <c r="H3">
-        <v>0.1137902559867878</v>
+        <v>0.196763827028246</v>
       </c>
       <c r="I3">
-        <v>0.2105147261216625</v>
+        <v>0.2025708969949822</v>
       </c>
       <c r="J3">
-        <v>0.1605769284269281</v>
+        <v>0.1515591642629319</v>
       </c>
       <c r="K3">
-        <v>256.6</v>
+        <v>256.3</v>
       </c>
       <c r="L3">
-        <v>0.1412606661161575</v>
+        <v>0.1445001973276202</v>
       </c>
       <c r="M3">
-        <v>112.3</v>
+        <v>222.23</v>
       </c>
       <c r="N3">
-        <v>0.05288438898045679</v>
+        <v>0.1148831679073614</v>
       </c>
       <c r="O3">
-        <v>0.4376461418550272</v>
+        <v>0.8670698400312133</v>
       </c>
       <c r="P3">
-        <v>95</v>
+        <v>219.7</v>
       </c>
       <c r="Q3">
-        <v>0.0447374617376972</v>
+        <v>0.1135752688172043</v>
       </c>
       <c r="R3">
-        <v>0.3702260327357755</v>
+        <v>0.8571985953960202</v>
       </c>
       <c r="S3">
-        <v>17.3</v>
+        <v>2.530000000000001</v>
       </c>
       <c r="T3">
-        <v>0.1540516473731077</v>
+        <v>0.01138460153894614</v>
       </c>
       <c r="U3">
-        <v>371.6</v>
+        <v>704</v>
       </c>
       <c r="V3">
-        <v>0.1749941134918766</v>
+        <v>0.3639371381306865</v>
       </c>
       <c r="W3">
-        <v>0.1122975929978118</v>
+        <v>0.1071801948730816</v>
       </c>
       <c r="X3">
-        <v>0.09564319545312612</v>
+        <v>0.1493918435640297</v>
       </c>
       <c r="Y3">
-        <v>0.0166543975446857</v>
+        <v>-0.04221164869094809</v>
       </c>
       <c r="Z3">
-        <v>0.3924597601814843</v>
+        <v>0.3358071905942938</v>
       </c>
       <c r="AA3">
-        <v>0.06301998282111156</v>
+        <v>0.05089465715995425</v>
       </c>
       <c r="AB3">
-        <v>0.0511238407241796</v>
+        <v>0.07889805559136959</v>
       </c>
       <c r="AC3">
-        <v>0.01189614209693195</v>
+        <v>-0.02800339843141534</v>
       </c>
       <c r="AD3">
-        <v>3441.8</v>
+        <v>3506.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3441.8</v>
+        <v>3506.1</v>
       </c>
       <c r="AG3">
-        <v>3070.2</v>
+        <v>2802.1</v>
       </c>
       <c r="AH3">
-        <v>0.6184392575422709</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="AI3">
-        <v>0.5900059998285764</v>
+        <v>0.6462618889626189</v>
       </c>
       <c r="AJ3">
-        <v>0.5911392648786029</v>
+        <v>0.5915971709067877</v>
       </c>
       <c r="AK3">
-        <v>0.5621120855379997</v>
+        <v>0.59351436075574</v>
       </c>
       <c r="AL3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AM3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AN3">
-        <v>8.623903783512905</v>
+        <v>9.658677685950414</v>
       </c>
       <c r="AO3">
-        <v>16.62608695652174</v>
+        <v>13.30740740740741</v>
       </c>
       <c r="AP3">
-        <v>7.692808819844651</v>
+        <v>7.719283746556473</v>
       </c>
       <c r="AQ3">
-        <v>16.62608695652174</v>
+        <v>13.30740740740741</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/france/france_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0522</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="E2">
-        <v>0.261</v>
+        <v>0.178</v>
       </c>
       <c r="F2">
-        <v>-0.03759999999999999</v>
+        <v>-0.0398</v>
       </c>
       <c r="G2">
-        <v>0.196763827028246</v>
+        <v>0.2390634928393372</v>
       </c>
       <c r="H2">
-        <v>0.196763827028246</v>
+        <v>0.2390634928393372</v>
       </c>
       <c r="I2">
-        <v>0.2025708969949822</v>
+        <v>0.234517816120045</v>
       </c>
       <c r="J2">
-        <v>0.1515591642629319</v>
+        <v>0.1776579215656215</v>
       </c>
       <c r="K2">
-        <v>256.3</v>
+        <v>303.8</v>
       </c>
       <c r="L2">
-        <v>0.1445001973276202</v>
+        <v>0.1484921061635466</v>
       </c>
       <c r="M2">
-        <v>222.23</v>
+        <v>247.01</v>
       </c>
       <c r="N2">
-        <v>0.1148831679073614</v>
+        <v>0.1267628040644565</v>
       </c>
       <c r="O2">
-        <v>0.8670698400312133</v>
+        <v>0.8130678077682686</v>
       </c>
       <c r="P2">
-        <v>219.7</v>
+        <v>240.2</v>
       </c>
       <c r="Q2">
-        <v>0.1135752688172043</v>
+        <v>0.1232679872729139</v>
       </c>
       <c r="R2">
-        <v>0.8571985953960202</v>
+        <v>0.7906517445687952</v>
       </c>
       <c r="S2">
-        <v>2.530000000000001</v>
+        <v>6.810000000000002</v>
       </c>
       <c r="T2">
-        <v>0.01138460153894614</v>
+        <v>0.02756973401886564</v>
       </c>
       <c r="U2">
-        <v>704</v>
+        <v>570.2</v>
       </c>
       <c r="V2">
-        <v>0.3639371381306865</v>
+        <v>0.2926203428102228</v>
       </c>
       <c r="W2">
-        <v>0.1071801948730816</v>
+        <v>0.158451989777291</v>
       </c>
       <c r="X2">
-        <v>0.1493918435640297</v>
+        <v>0.1261463689574133</v>
       </c>
       <c r="Y2">
-        <v>-0.04221164869094809</v>
+        <v>0.03230562081987773</v>
       </c>
       <c r="Z2">
-        <v>0.3358071905942938</v>
+        <v>0.4481512310523088</v>
       </c>
       <c r="AA2">
-        <v>0.05089465715995425</v>
+        <v>0.07961761625582779</v>
       </c>
       <c r="AB2">
-        <v>0.07889805559136959</v>
+        <v>0.06745034409285</v>
       </c>
       <c r="AC2">
-        <v>-0.02800339843141534</v>
+        <v>0.01216727216297779</v>
       </c>
       <c r="AD2">
-        <v>3506.1</v>
+        <v>3859.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3506.1</v>
+        <v>3859.5</v>
       </c>
       <c r="AG2">
-        <v>2802.1</v>
+        <v>3289.3</v>
       </c>
       <c r="AH2">
-        <v>0.6444444444444444</v>
+        <v>0.6645030216421893</v>
       </c>
       <c r="AI2">
-        <v>0.6462618889626189</v>
+        <v>0.6474258970358814</v>
       </c>
       <c r="AJ2">
-        <v>0.5915971709067877</v>
+        <v>0.6279806792798641</v>
       </c>
       <c r="AK2">
-        <v>0.59351436075574</v>
+        <v>0.6101352228673184</v>
       </c>
       <c r="AL2">
-        <v>27</v>
+        <v>34.5</v>
       </c>
       <c r="AM2">
-        <v>27</v>
+        <v>34.5</v>
       </c>
       <c r="AN2">
-        <v>9.658677685950414</v>
+        <v>7.9007164790174</v>
       </c>
       <c r="AO2">
-        <v>13.30740740740741</v>
+        <v>13.90724637681159</v>
       </c>
       <c r="AP2">
-        <v>7.719283746556473</v>
+        <v>6.733469805527124</v>
       </c>
       <c r="AQ2">
-        <v>13.30740740740741</v>
+        <v>13.90724637681159</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0522</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="E3">
-        <v>0.261</v>
+        <v>0.178</v>
       </c>
       <c r="F3">
-        <v>-0.03759999999999999</v>
+        <v>-0.0398</v>
       </c>
       <c r="G3">
-        <v>0.196763827028246</v>
+        <v>0.2390634928393372</v>
       </c>
       <c r="H3">
-        <v>0.196763827028246</v>
+        <v>0.2390634928393372</v>
       </c>
       <c r="I3">
-        <v>0.2025708969949822</v>
+        <v>0.234517816120045</v>
       </c>
       <c r="J3">
-        <v>0.1515591642629319</v>
+        <v>0.1776579215656215</v>
       </c>
       <c r="K3">
-        <v>256.3</v>
+        <v>303.8</v>
       </c>
       <c r="L3">
-        <v>0.1445001973276202</v>
+        <v>0.1484921061635466</v>
       </c>
       <c r="M3">
-        <v>222.23</v>
+        <v>247.01</v>
       </c>
       <c r="N3">
-        <v>0.1148831679073614</v>
+        <v>0.1267628040644565</v>
       </c>
       <c r="O3">
-        <v>0.8670698400312133</v>
+        <v>0.8130678077682686</v>
       </c>
       <c r="P3">
-        <v>219.7</v>
+        <v>240.2</v>
       </c>
       <c r="Q3">
-        <v>0.1135752688172043</v>
+        <v>0.1232679872729139</v>
       </c>
       <c r="R3">
-        <v>0.8571985953960202</v>
+        <v>0.7906517445687952</v>
       </c>
       <c r="S3">
-        <v>2.530000000000001</v>
+        <v>6.810000000000002</v>
       </c>
       <c r="T3">
-        <v>0.01138460153894614</v>
+        <v>0.02756973401886564</v>
       </c>
       <c r="U3">
-        <v>704</v>
+        <v>570.2</v>
       </c>
       <c r="V3">
-        <v>0.3639371381306865</v>
+        <v>0.2926203428102228</v>
       </c>
       <c r="W3">
-        <v>0.1071801948730816</v>
+        <v>0.158451989777291</v>
       </c>
       <c r="X3">
-        <v>0.1493918435640297</v>
+        <v>0.1261463689574133</v>
       </c>
       <c r="Y3">
-        <v>-0.04221164869094809</v>
+        <v>0.03230562081987773</v>
       </c>
       <c r="Z3">
-        <v>0.3358071905942938</v>
+        <v>0.4481512310523088</v>
       </c>
       <c r="AA3">
-        <v>0.05089465715995425</v>
+        <v>0.07961761625582779</v>
       </c>
       <c r="AB3">
-        <v>0.07889805559136959</v>
+        <v>0.06745034409285</v>
       </c>
       <c r="AC3">
-        <v>-0.02800339843141534</v>
+        <v>0.01216727216297779</v>
       </c>
       <c r="AD3">
-        <v>3506.1</v>
+        <v>3859.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3506.1</v>
+        <v>3859.5</v>
       </c>
       <c r="AG3">
-        <v>2802.1</v>
+        <v>3289.3</v>
       </c>
       <c r="AH3">
-        <v>0.6444444444444444</v>
+        <v>0.6645030216421893</v>
       </c>
       <c r="AI3">
-        <v>0.6462618889626189</v>
+        <v>0.6474258970358814</v>
       </c>
       <c r="AJ3">
-        <v>0.5915971709067877</v>
+        <v>0.6279806792798641</v>
       </c>
       <c r="AK3">
-        <v>0.59351436075574</v>
+        <v>0.6101352228673184</v>
       </c>
       <c r="AL3">
-        <v>27</v>
+        <v>34.5</v>
       </c>
       <c r="AM3">
-        <v>27</v>
+        <v>34.5</v>
       </c>
       <c r="AN3">
-        <v>9.658677685950414</v>
+        <v>7.9007164790174</v>
       </c>
       <c r="AO3">
-        <v>13.30740740740741</v>
+        <v>13.90724637681159</v>
       </c>
       <c r="AP3">
-        <v>7.719283746556473</v>
+        <v>6.733469805527124</v>
       </c>
       <c r="AQ3">
-        <v>13.30740740740741</v>
+        <v>13.90724637681159</v>
       </c>
     </row>
   </sheetData>
